--- a/data/trans_orig/P2B_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18424</t>
+          <t>18599</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31305</t>
+          <t>32047</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19031</t>
+          <t>19262</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31715</t>
+          <t>32297</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41339</t>
+          <t>41004</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59567</t>
+          <t>58898</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>48408</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62031</t>
+          <t>61856</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39922</t>
+          <t>39340</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52606</t>
+          <t>52375</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92525</t>
+          <t>93194</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110753</t>
+          <t>111088</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>73,04%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18929</t>
+          <t>18299</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31026</t>
+          <t>30753</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15851</t>
+          <t>15581</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28242</t>
+          <t>28178</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37911</t>
+          <t>37122</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56140</t>
+          <t>54438</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>39,98%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37661</t>
+          <t>37934</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49758</t>
+          <t>50388</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39243</t>
+          <t>39307</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51634</t>
+          <t>51904</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>80032</t>
+          <t>81734</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>98261</t>
+          <t>99050</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,74%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>11787</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21888</t>
+          <t>22089</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17360</t>
+          <t>17891</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30854</t>
+          <t>31522</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32616</t>
+          <t>32187</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49503</t>
+          <t>49398</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36357</t>
+          <t>36156</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46659</t>
+          <t>46458</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53090</t>
+          <t>52422</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66584</t>
+          <t>66053</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>92686</t>
+          <t>92791</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>109573</t>
+          <t>110002</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,36%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36004</t>
+          <t>37143</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53428</t>
+          <t>53470</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37735</t>
+          <t>36253</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55612</t>
+          <t>56217</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78938</t>
+          <t>78911</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103892</t>
+          <t>103746</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97868</t>
+          <t>97826</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115292</t>
+          <t>114153</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>92950</t>
+          <t>92345</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>110827</t>
+          <t>112309</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>195966</t>
+          <t>196112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>220920</t>
+          <t>220947</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18364</t>
+          <t>18562</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32514</t>
+          <t>31462</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21512</t>
+          <t>21862</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34992</t>
+          <t>34798</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41681</t>
+          <t>42821</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61620</t>
+          <t>61786</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,21%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36609</t>
+          <t>37661</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50759</t>
+          <t>50561</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49538</t>
+          <t>49732</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63018</t>
+          <t>62668</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>92032</t>
+          <t>91866</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>111971</t>
+          <t>110831</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,13%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17456</t>
+          <t>16951</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31293</t>
+          <t>30272</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10268</t>
+          <t>10452</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21026</t>
+          <t>21322</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30361</t>
+          <t>29753</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47866</t>
+          <t>48241</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43577</t>
+          <t>44598</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57414</t>
+          <t>57919</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51366</t>
+          <t>51070</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62124</t>
+          <t>61940</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99396</t>
+          <t>99021</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>116901</t>
+          <t>117509</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,8%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>141785</t>
+          <t>141107</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>174921</t>
+          <t>174680</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>141508</t>
+          <t>145465</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>176911</t>
+          <t>180130</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>296495</t>
+          <t>294891</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>342452</t>
+          <t>342826</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,24%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>327754</t>
+          <t>327995</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>360890</t>
+          <t>361568</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>351638</t>
+          <t>348419</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>387041</t>
+          <t>383084</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>688773</t>
+          <t>688399</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>734730</t>
+          <t>736334</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,4%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43269</t>
+          <t>44373</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54466</t>
+          <t>54312</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52461</t>
+          <t>52994</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63900</t>
+          <t>64231</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100278</t>
+          <t>101050</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115385</t>
+          <t>115993</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>86,16%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6909</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17952</t>
+          <t>16848</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20949</t>
+          <t>20416</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19246</t>
+          <t>18638</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34353</t>
+          <t>33581</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45076</t>
+          <t>44952</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56366</t>
+          <t>56154</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51640</t>
+          <t>51969</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62034</t>
+          <t>61937</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>101734</t>
+          <t>100787</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116294</t>
+          <t>115579</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,31%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9013</t>
+          <t>9225</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20303</t>
+          <t>20427</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16886</t>
+          <t>16557</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17611</t>
+          <t>18326</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32171</t>
+          <t>33118</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49727</t>
+          <t>49467</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59815</t>
+          <t>59950</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51643</t>
+          <t>51194</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60856</t>
+          <t>60915</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>104432</t>
+          <t>105115</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118276</t>
+          <t>118480</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,1%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>6573</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16796</t>
+          <t>17056</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16321</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16211</t>
+          <t>16007</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30055</t>
+          <t>29372</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>104005</t>
+          <t>104027</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119281</t>
+          <t>119691</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>132403</t>
+          <t>132138</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146143</t>
+          <t>146008</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>242742</t>
+          <t>241919</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>261726</t>
+          <t>261744</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,07%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17199</t>
+          <t>16789</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32475</t>
+          <t>32453</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14591</t>
+          <t>14726</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28331</t>
+          <t>28596</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35488</t>
+          <t>35470</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54472</t>
+          <t>55295</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74290</t>
+          <t>74147</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85886</t>
+          <t>85766</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67432</t>
+          <t>66662</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79646</t>
+          <t>80036</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>144950</t>
+          <t>146167</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163222</t>
+          <t>163403</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,11%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19161</t>
+          <t>19304</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12362</t>
+          <t>11972</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24576</t>
+          <t>25346</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22237</t>
+          <t>22056</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40509</t>
+          <t>39292</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37780</t>
+          <t>37720</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47159</t>
+          <t>47606</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54117</t>
+          <t>54973</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65596</t>
+          <t>65676</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>95875</t>
+          <t>95994</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>110472</t>
+          <t>110309</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,21%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16131</t>
+          <t>16191</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19921</t>
+          <t>19065</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>17640</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32074</t>
+          <t>31955</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>379315</t>
+          <t>380002</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>407294</t>
+          <t>407906</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>432661</t>
+          <t>434523</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>462950</t>
+          <t>461623</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>822918</t>
+          <t>821446</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>861110</t>
+          <t>861414</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,98%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>69671</t>
+          <t>69059</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>97650</t>
+          <t>96963</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>73730</t>
+          <t>75057</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>104019</t>
+          <t>102157</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>152534</t>
+          <t>152230</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>190726</t>
+          <t>192198</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36625</t>
+          <t>36552</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49205</t>
+          <t>49363</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56249</t>
+          <t>55894</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67678</t>
+          <t>67758</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97391</t>
+          <t>97468</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114293</t>
+          <t>114881</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>81,08%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14900</t>
+          <t>14742</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27480</t>
+          <t>27553</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9897</t>
+          <t>9817</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21326</t>
+          <t>21681</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27387</t>
+          <t>26799</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44289</t>
+          <t>44212</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,21%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54753</t>
+          <t>54855</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67005</t>
+          <t>66562</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52697</t>
+          <t>52192</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67324</t>
+          <t>67017</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>111637</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>130353</t>
+          <t>130995</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,81%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>13907</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25716</t>
+          <t>25614</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22750</t>
+          <t>23057</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37377</t>
+          <t>37882</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40190</t>
+          <t>39548</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>59591</t>
+          <t>58906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28066</t>
+          <t>28237</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38603</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32542</t>
+          <t>33488</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44770</t>
+          <t>46047</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65478</t>
+          <t>64256</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80692</t>
+          <t>80950</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,9%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>10621</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21158</t>
+          <t>20987</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15541</t>
+          <t>14264</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27769</t>
+          <t>26823</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28843</t>
+          <t>28585</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44057</t>
+          <t>45279</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>41,34%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>101679</t>
+          <t>102726</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121308</t>
+          <t>121314</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105923</t>
+          <t>107032</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126145</t>
+          <t>126285</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>213630</t>
+          <t>213651</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>240819</t>
+          <t>241224</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,83%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38814</t>
+          <t>38808</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58443</t>
+          <t>57396</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40477</t>
+          <t>40337</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60699</t>
+          <t>59590</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85925</t>
+          <t>85520</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>113114</t>
+          <t>113093</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58708</t>
+          <t>58322</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73571</t>
+          <t>73988</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63217</t>
+          <t>63871</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>78444</t>
+          <t>78098</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126151</t>
+          <t>125437</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>148186</t>
+          <t>148667</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,55%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27363</t>
+          <t>26946</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42226</t>
+          <t>42612</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20039</t>
+          <t>20385</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35266</t>
+          <t>34612</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51231</t>
+          <t>50750</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73266</t>
+          <t>73980</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>37,1%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27640</t>
+          <t>28026</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40284</t>
+          <t>40244</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33912</t>
+          <t>34090</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47902</t>
+          <t>47298</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64915</t>
+          <t>65963</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83974</t>
+          <t>83457</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,36%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19573</t>
+          <t>19613</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>31831</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19923</t>
+          <t>20527</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33913</t>
+          <t>33735</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>43708</t>
+          <t>44225</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>62767</t>
+          <t>61719</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>332609</t>
+          <t>332999</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>367263</t>
+          <t>366840</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>372914</t>
+          <t>372225</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>409425</t>
+          <t>407856</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>715618</t>
+          <t>716448</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>766196</t>
+          <t>765546</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,17%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>147448</t>
+          <t>147871</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>182102</t>
+          <t>181712</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>151465</t>
+          <t>153034</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>187976</t>
+          <t>188665</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>309405</t>
+          <t>310055</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>359983</t>
+          <t>359153</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18815</t>
+          <t>18600</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>32704</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26935</t>
+          <t>26828</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47478</t>
+          <t>47347</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50739</t>
+          <t>50297</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75243</t>
+          <t>74648</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,01%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71131</t>
+          <t>71758</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85647</t>
+          <t>85862</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88772</t>
+          <t>88903</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>109315</t>
+          <t>109422</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>165469</t>
+          <t>166064</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>189973</t>
+          <t>190415</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,1%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>24659</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40663</t>
+          <t>39963</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21354</t>
+          <t>21113</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36574</t>
+          <t>36771</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50131</t>
+          <t>51115</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71650</t>
+          <t>73045</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,63%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53429</t>
+          <t>54129</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69312</t>
+          <t>69433</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58421</t>
+          <t>58224</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>73641</t>
+          <t>73882</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>117436</t>
+          <t>116041</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>138955</t>
+          <t>137971</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>72,97%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11579</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23599</t>
+          <t>23723</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16300</t>
+          <t>15680</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30038</t>
+          <t>29850</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31019</t>
+          <t>31617</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49406</t>
+          <t>49970</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28262</t>
+          <t>28138</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40282</t>
+          <t>40064</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33815</t>
+          <t>34003</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47553</t>
+          <t>48173</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66308</t>
+          <t>65744</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>84695</t>
+          <t>84097</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39155</t>
+          <t>37425</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73537</t>
+          <t>73707</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54025</t>
+          <t>53038</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80356</t>
+          <t>79545</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94449</t>
+          <t>97432</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143962</t>
+          <t>143117</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143282</t>
+          <t>143112</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177664</t>
+          <t>179394</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>136495</t>
+          <t>137306</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>162826</t>
+          <t>163813</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>289708</t>
+          <t>290553</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>339221</t>
+          <t>336238</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>77,53%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31941</t>
+          <t>32900</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49862</t>
+          <t>50103</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55923</t>
+          <t>55462</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89075</t>
+          <t>89837</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93505</t>
+          <t>93253</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>132975</t>
+          <t>132430</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>46,95%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69566</t>
+          <t>69325</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87487</t>
+          <t>86528</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73542</t>
+          <t>72780</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>106694</t>
+          <t>107155</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>149070</t>
+          <t>149615</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>188540</t>
+          <t>188792</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,94%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21800</t>
+          <t>22010</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36174</t>
+          <t>36402</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>27423</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43704</t>
+          <t>43397</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>53759</t>
+          <t>53204</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75531</t>
+          <t>75119</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,31%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32721</t>
+          <t>32493</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47095</t>
+          <t>46885</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28299</t>
+          <t>28606</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44318</t>
+          <t>44580</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>65367</t>
+          <t>65779</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87139</t>
+          <t>87694</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>62,24%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>171095</t>
+          <t>170764</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>224495</t>
+          <t>223411</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>232476</t>
+          <t>231341</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>286917</t>
+          <t>284751</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>419406</t>
+          <t>416117</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>498355</t>
+          <t>497487</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,48%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>431061</t>
+          <t>432145</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>484461</t>
+          <t>484792</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>459652</t>
+          <t>461818</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>514093</t>
+          <t>515228</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>903770</t>
+          <t>904638</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>982719</t>
+          <t>986008</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,32%</t>
         </is>
       </c>
     </row>
